--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_SCB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_SCB.xlsx
@@ -13,8 +13,8 @@
     <sheet name="duos_trios" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$A$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -458,7 +458,11 @@
           <t>team_name</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sporting Clube Braga</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -468,36 +472,72 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>best_duo</t>
+          <t>primary_scorer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Sibert | R. Monteiro (5.1 net)</t>
+          <t>A. Gakou (22 ppg)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>most_used_player</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>R. Monteiro (28.0 mpg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>best_3pt_pct</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M. Correia (66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>best_duo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>J. Sibert | R. Monteiro (22.4 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>best_trio</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>C. Cardoso | J. Sibert | R. Monteiro (0 net)</t>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A. Gakou | J. Sibert | R. Monteiro (37.9 net)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -508,28 +548,710 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="41" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>playing_position</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>games_started</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>minutes_total</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>rpg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>apg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tov_pg</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>spg</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>bpg</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>tp_pct</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ft_pct</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>efg_pct</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ts_pct</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>plus_minus_pg</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>on_off_net_diff_per40</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>role_tag</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>Sporting Clube Braga</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>R. Monteiro</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>56</v>
+      </c>
+      <c r="G2" t="n">
+        <v>28</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>71.4%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>63.3%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>66.4%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>high-minutes, primary-scorer, efficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Sporting Clube Braga</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>J. Sibert</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>88.9%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>54.6%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>high-minutes, primary-scorer, impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sporting Clube Braga</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>A. Gakou</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="G4" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>22</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>59.3%</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>74.1%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>73.1%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>16</v>
+      </c>
+      <c r="T4" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>high-minutes, primary-scorer, efficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Sporting Clube Braga</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>M. Correia</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>79.0%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-3.5</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>high-minutes, efficient, shooter</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Sporting Clube Braga</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>V. Panov</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>47.2%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>-9</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-55.8</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sporting Clube Braga</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>A. Silva</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>22</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>12</v>
+      </c>
+      <c r="T7" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>primary-scorer, efficient, shooter</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sporting Clube Braga</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>C. Cardoso</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="H8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>56.7%</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-15.8</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>shooter</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:U8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -661,22 +1383,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
-        <v>23.6</v>
+        <v>41.1</v>
       </c>
       <c r="H2" t="n">
-        <v>93</v>
+        <v>101.1</v>
       </c>
       <c r="I2" t="n">
-        <v>87.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="3">
@@ -697,26 +1419,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>M. Correia | R. Monteiro</t>
+          <t>A. Silva | R. Monteiro</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>19.6</v>
+        <v>32.1</v>
       </c>
       <c r="H3" t="n">
-        <v>77.40000000000001</v>
+        <v>109.5</v>
       </c>
       <c r="I3" t="n">
-        <v>69.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>8.1</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="4">
@@ -741,22 +1463,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>19.6</v>
+        <v>35.2</v>
       </c>
       <c r="H4" t="n">
-        <v>77.40000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="I4" t="n">
-        <v>69.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>8.1</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="5">
@@ -777,26 +1499,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>C. Cardoso | J. Sibert | R. Monteiro</t>
+          <t>A. Gakou | J. Sibert | R. Monteiro</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>16</v>
+        <v>27.5</v>
       </c>
       <c r="H5" t="n">
-        <v>92.7</v>
+        <v>115</v>
       </c>
       <c r="I5" t="n">
-        <v>92.7</v>
+        <v>77.2</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="6">
@@ -817,26 +1539,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A. Gakou | A. Silva | J. Sibert</t>
+          <t>A. Gakou | J. Sibert | R. Monteiro</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G6" t="n">
-        <v>14.1</v>
+        <v>27.5</v>
       </c>
       <c r="H6" t="n">
-        <v>110.5</v>
+        <v>115</v>
       </c>
       <c r="I6" t="n">
-        <v>93.5</v>
+        <v>77.2</v>
       </c>
       <c r="J6" t="n">
-        <v>17</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="7">
@@ -857,26 +1579,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>M. Correia | R. Monteiro | V. Panov</t>
+          <t>J. Sibert | M. Correia | R. Monteiro</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>13</v>
+        <v>24.7</v>
       </c>
       <c r="H7" t="n">
-        <v>80.2</v>
+        <v>100.5</v>
       </c>
       <c r="I7" t="n">
-        <v>67.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="J7" t="n">
-        <v>12.3</v>
+        <v>27.6</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_SCB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_SCB.xlsx
@@ -13,9 +13,9 @@
     <sheet name="duos_trios" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Gakou (22 ppg)</t>
+          <t>A. Gakou (19 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R. Monteiro (28.0 mpg)</t>
+          <t>R. Monteiro (26.0 mpg)</t>
         </is>
       </c>
     </row>
@@ -515,29 +515,53 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>best_duo</t>
+          <t>base_lineup</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Sibert | R. Monteiro (22.4 net)</t>
+          <t>A. Gakou | A. Moreira | C. Cardoso | J. Sibert | R. Monteiro (14.6 min)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>best_lineup</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A. Gakou | A. Moreira | C. Cardoso | J. Sibert | R. Monteiro (8.2 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>best_duo</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A. Gakou | J. Sibert (20.8 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>best_trio</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>A. Gakou | J. Sibert | R. Monteiro (37.9 net)</t>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A. Gakou | J. Sibert | R. Monteiro (31.6 net)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B9"/>
+  <autoFilter ref="A1:B11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -548,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -698,38 +722,38 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>56</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H2" t="n">
-        <v>12</v>
+        <v>11.3</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -744,23 +768,23 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="T2" t="n">
-        <v>17.4</v>
+        <v>11.7</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer, efficient</t>
+          <t>high-minutes, efficient, impact</t>
         </is>
       </c>
     </row>
@@ -772,74 +796,74 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J. Sibert</t>
+          <t>A. Gakou</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>55.3</v>
+        <v>74.3</v>
       </c>
       <c r="G3" t="n">
-        <v>27.7</v>
+        <v>24.8</v>
       </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>6.7</v>
       </c>
       <c r="J3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L3" t="n">
         <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>8.5</v>
+        <v>11.3</v>
       </c>
       <c r="T3" t="n">
-        <v>10.5</v>
+        <v>15.9</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer, impact</t>
+          <t>high-minutes, primary-scorer, efficient</t>
         </is>
       </c>
     </row>
@@ -851,74 +875,74 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A. Gakou</t>
+          <t>J. Sibert</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>52.2</v>
+        <v>72.3</v>
       </c>
       <c r="G4" t="n">
-        <v>26.1</v>
+        <v>24.1</v>
       </c>
       <c r="H4" t="n">
-        <v>22</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="J4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>0.5</v>
-      </c>
       <c r="L4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>74.1%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>16</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>42.6</v>
+        <v>-0.1</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>high-minutes, primary-scorer, efficient</t>
+          <t>high-minutes</t>
         </is>
       </c>
     </row>
@@ -939,38 +963,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>48.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>24.1</v>
+        <v>23.3</v>
       </c>
       <c r="H5" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -980,28 +1004,28 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>86.3%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>-3.5</v>
+        <v>3.7</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>high-minutes, efficient, shooter</t>
+          <t>efficient, shooter</t>
         </is>
       </c>
     </row>
@@ -1013,33 +1037,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>V. Panov</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>A. Silva</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>44.2</v>
+        <v>63.5</v>
       </c>
       <c r="G6" t="n">
-        <v>22.1</v>
+        <v>21.2</v>
       </c>
       <c r="H6" t="n">
-        <v>6.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1049,38 +1077,38 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>76.6%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>-9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-55.8</v>
+        <v>3.8</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>rotation</t>
+          <t>efficient, shooter</t>
         </is>
       </c>
     </row>
@@ -1092,7 +1120,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A. Silva</t>
+          <t>C. Cardoso</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1101,69 +1129,69 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>44.1</v>
+        <v>62.2</v>
       </c>
       <c r="G7" t="n">
-        <v>22</v>
+        <v>20.7</v>
       </c>
       <c r="H7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T7" t="n">
-        <v>21.1</v>
+        <v>-2.3</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>primary-scorer, efficient, shooter</t>
+          <t>efficient, shooter</t>
         </is>
       </c>
     </row>
@@ -1175,83 +1203,162 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C. Cardoso</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
+          <t>V. Panov</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>41.4</v>
+        <v>62.1</v>
       </c>
       <c r="G8" t="n">
         <v>20.7</v>
       </c>
       <c r="H8" t="n">
-        <v>10.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
+          <t>47.4%</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>40.0%</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>52.6%</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>57.7%</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-27.6</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>shooter</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Sporting Clube Braga</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>A. Moreira</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>44</v>
+      </c>
+      <c r="G9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>40.0%</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>87.5%</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>46.7%</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>56.7%</t>
-        </is>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-15.8</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>shooter</t>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>43.3%</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>46.0%</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-18.2</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>rotation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U8"/>
+  <autoFilter ref="A1:U9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1262,28 +1369,219 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>lineup_players</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>stints</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pf_per40</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pa_per40</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>net_per40</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>team_rank_minutes</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>team_rank_net</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>team_rank_defense</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>Base lineup</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Sporting Clube Braga</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>A. Gakou | A. Moreira | C. Cardoso | J. Sibert | R. Monteiro</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>74</v>
+      </c>
+      <c r="H2" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>23</v>
+      </c>
+      <c r="L2" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Best lineup</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sporting Clube Braga</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A. Gakou | A. Moreira | C. Cardoso | J. Sibert | R. Monteiro</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>74</v>
+      </c>
+      <c r="H3" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>23</v>
+      </c>
+      <c r="L3" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Best defense</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Sporting Clube Braga</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>A. Gakou | A. Moreira | C. Cardoso | J. Sibert | R. Monteiro</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>74</v>
+      </c>
+      <c r="H4" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>23</v>
+      </c>
+      <c r="L4" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:L4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1300,7 +1598,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -1379,26 +1677,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>J. Sibert | R. Monteiro</t>
+          <t>A. Gakou | J. Sibert</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>41.1</v>
+        <v>53.9</v>
       </c>
       <c r="H2" t="n">
-        <v>101.1</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>78.7</v>
+        <v>77.3</v>
       </c>
       <c r="J2" t="n">
-        <v>22.4</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="3">
@@ -1419,26 +1717,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A. Silva | R. Monteiro</t>
+          <t>A. Gakou | R. Monteiro</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G3" t="n">
-        <v>32.1</v>
+        <v>47.5</v>
       </c>
       <c r="H3" t="n">
-        <v>109.5</v>
+        <v>101.1</v>
       </c>
       <c r="I3" t="n">
-        <v>78.40000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="J3" t="n">
-        <v>31.1</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="4">
@@ -1459,26 +1757,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>M. Correia | R. Monteiro</t>
+          <t>A. Gakou | R. Monteiro</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>35.2</v>
+        <v>47.5</v>
       </c>
       <c r="H4" t="n">
-        <v>98.8</v>
+        <v>101.1</v>
       </c>
       <c r="I4" t="n">
-        <v>74.90000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="J4" t="n">
-        <v>23.8</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="5">
@@ -1503,22 +1801,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G5" t="n">
-        <v>27.5</v>
+        <v>39.3</v>
       </c>
       <c r="H5" t="n">
-        <v>115</v>
+        <v>102.9</v>
       </c>
       <c r="I5" t="n">
-        <v>77.2</v>
+        <v>71.3</v>
       </c>
       <c r="J5" t="n">
-        <v>37.9</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="6">
@@ -1539,26 +1837,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A. Gakou | J. Sibert | R. Monteiro</t>
+          <t>A. Gakou | C. Cardoso | R. Monteiro</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>27.5</v>
+        <v>28.1</v>
       </c>
       <c r="H6" t="n">
-        <v>115</v>
+        <v>100.9</v>
       </c>
       <c r="I6" t="n">
-        <v>77.2</v>
+        <v>63.9</v>
       </c>
       <c r="J6" t="n">
-        <v>37.9</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="7">
@@ -1579,26 +1877,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>J. Sibert | M. Correia | R. Monteiro</t>
+          <t>A. Gakou | C. Cardoso | R. Monteiro</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="G7" t="n">
-        <v>24.7</v>
+        <v>28.1</v>
       </c>
       <c r="H7" t="n">
-        <v>100.5</v>
+        <v>100.9</v>
       </c>
       <c r="I7" t="n">
-        <v>73</v>
+        <v>63.9</v>
       </c>
       <c r="J7" t="n">
-        <v>27.6</v>
+        <v>36.9</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_SCB.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_SCB.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A. Gakou (19 ppg)</t>
+          <t>A. Gakou (18.8 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R. Monteiro (26.0 mpg)</t>
+          <t>R. Monteiro (26.2 mpg)</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M. Correia (66.7%)</t>
+          <t>M. Correia (53.8%)</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A. Gakou | A. Moreira | C. Cardoso | J. Sibert | R. Monteiro (14.6 min)</t>
+          <t>A. Gakou | C. Cardoso | J. Sibert | M. Kegler | R. Monteiro (15.3 min)</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A. Gakou | A. Moreira | C. Cardoso | J. Sibert | R. Monteiro (8.2 net)</t>
+          <t>A. Gakou | C. Cardoso | J. Sibert | M. Kegler | R. Monteiro (26.2 net)</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A. Gakou | J. Sibert (20.8 net)</t>
+          <t>A. Gakou | J. Sibert (19.9 net)</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A. Gakou | J. Sibert | R. Monteiro (31.6 net)</t>
+          <t>A. Gakou | J. Sibert | R. Monteiro (29.1 net)</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -722,65 +722,65 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>78.09999999999999</v>
+        <v>105</v>
       </c>
       <c r="G2" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="H2" t="n">
-        <v>11.3</v>
+        <v>10.2</v>
       </c>
       <c r="I2" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>12.2</v>
       </c>
       <c r="T2" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -799,67 +799,71 @@
           <t>A. Gakou</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>74.3</v>
+        <v>101.3</v>
       </c>
       <c r="G3" t="n">
-        <v>24.8</v>
+        <v>25.3</v>
       </c>
       <c r="H3" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="I3" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>11.3</v>
+        <v>11.8</v>
       </c>
       <c r="T3" t="n">
-        <v>15.9</v>
+        <v>18.3</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -880,69 +884,69 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>72.3</v>
+        <v>98</v>
       </c>
       <c r="G4" t="n">
-        <v>24.1</v>
+        <v>24.5</v>
       </c>
       <c r="H4" t="n">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>26.7%</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>8.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1</v>
+        <v>10.5</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>high-minutes</t>
+          <t>high-minutes, impact</t>
         </is>
       </c>
     </row>
@@ -963,65 +967,65 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>69.90000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="G5" t="n">
-        <v>23.3</v>
+        <v>21.6</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>3.7</v>
+        <v>-5.5</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1046,69 +1050,69 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>63.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>21.2</v>
+        <v>20.6</v>
       </c>
       <c r="H6" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="T6" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>efficient, shooter</t>
+          <t>efficient, shooter, impact</t>
         </is>
       </c>
     </row>
@@ -1129,43 +1133,43 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>62.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1175,23 +1179,23 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>-2.3</v>
+        <v>-6.2</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>efficient, shooter</t>
+          <t>rotation</t>
         </is>
       </c>
     </row>
@@ -1206,71 +1210,75 @@
           <t>V. Panov</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>62.1</v>
+        <v>73.3</v>
       </c>
       <c r="G8" t="n">
-        <v>20.7</v>
+        <v>18.3</v>
       </c>
       <c r="H8" t="n">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>-0.3</v>
+        <v>-1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>-27.6</v>
+        <v>-26.6</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>shooter</t>
+          <t>efficient, shooter</t>
         </is>
       </c>
     </row>
@@ -1291,74 +1299,153 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>44</v>
+        <v>58.8</v>
       </c>
       <c r="G9" t="n">
         <v>14.7</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>35.3%</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>38.2%</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>40.9%</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-26.9</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Sporting Clube Braga</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>M. Kegler</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>57</v>
+      </c>
+      <c r="G10" t="n">
+        <v>19</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
         <v>1.3</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
         <v>0.3</v>
       </c>
-      <c r="M9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>43.3%</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>46.0%</t>
-        </is>
-      </c>
-      <c r="S9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-18.2</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>rotation</t>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>67.5%</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>68.9%</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="T10" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>efficient, shooter, impact</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U9"/>
+  <autoFilter ref="A1:U10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1369,10 +1456,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -1461,26 +1548,26 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A. Gakou | A. Moreira | C. Cardoso | J. Sibert | R. Monteiro</t>
+          <t>A. Gakou | C. Cardoso | J. Sibert | M. Kegler | R. Monteiro</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="G2" t="n">
-        <v>74</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>65.8</v>
+        <v>62.9</v>
       </c>
       <c r="I2" t="n">
-        <v>8.199999999999999</v>
+        <v>26.2</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -1489,7 +1576,7 @@
         <v>23</v>
       </c>
       <c r="L2" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -1505,26 +1592,26 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A. Gakou | A. Moreira | C. Cardoso | J. Sibert | R. Monteiro</t>
+          <t>A. Gakou | C. Cardoso | J. Sibert | M. Kegler | R. Monteiro</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="G3" t="n">
-        <v>74</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>65.8</v>
+        <v>62.9</v>
       </c>
       <c r="I3" t="n">
-        <v>8.199999999999999</v>
+        <v>26.2</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -1533,7 +1620,7 @@
         <v>23</v>
       </c>
       <c r="L3" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -1549,26 +1636,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A. Gakou | A. Moreira | C. Cardoso | J. Sibert | R. Monteiro</t>
+          <t>A. Gakou | C. Cardoso | J. Sibert | M. Kegler | R. Monteiro</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="G4" t="n">
-        <v>74</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>65.8</v>
+        <v>62.9</v>
       </c>
       <c r="I4" t="n">
-        <v>8.199999999999999</v>
+        <v>26.2</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -1577,11 +1664,55 @@
         <v>23</v>
       </c>
       <c r="L4" t="n">
-        <v>20</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Rotation lineup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sporting Clube Braga</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>A. Gakou | A. Moreira | C. Cardoso | J. Sibert | R. Monteiro</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>71</v>
+      </c>
+      <c r="H5" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>29</v>
+      </c>
+      <c r="L5" t="n">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L4"/>
+  <autoFilter ref="A1:L5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1681,22 +1812,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>53.9</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>98.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="I2" t="n">
-        <v>77.3</v>
+        <v>74.3</v>
       </c>
       <c r="J2" t="n">
-        <v>20.8</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="3">
@@ -1717,26 +1848,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A. Gakou | R. Monteiro</t>
+          <t>A. Silva | J. Sibert</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G3" t="n">
-        <v>47.5</v>
+        <v>40.7</v>
       </c>
       <c r="H3" t="n">
-        <v>101.1</v>
+        <v>108.1</v>
       </c>
       <c r="I3" t="n">
-        <v>70.7</v>
+        <v>72.7</v>
       </c>
       <c r="J3" t="n">
-        <v>30.3</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="4">
@@ -1761,22 +1892,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>47.5</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>101.1</v>
+        <v>94.2</v>
       </c>
       <c r="I4" t="n">
-        <v>70.7</v>
+        <v>67.7</v>
       </c>
       <c r="J4" t="n">
-        <v>30.3</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="5">
@@ -1801,22 +1932,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G5" t="n">
-        <v>39.3</v>
+        <v>56.4</v>
       </c>
       <c r="H5" t="n">
-        <v>102.9</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>71.3</v>
+        <v>67.3</v>
       </c>
       <c r="J5" t="n">
-        <v>31.6</v>
+        <v>29.1</v>
       </c>
     </row>
     <row r="6">
@@ -1837,26 +1968,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>A. Gakou | C. Cardoso | R. Monteiro</t>
+          <t>A. Gakou | A. Silva | J. Sibert</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
         <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>28.1</v>
+        <v>31.2</v>
       </c>
       <c r="H6" t="n">
-        <v>100.9</v>
+        <v>114</v>
       </c>
       <c r="I6" t="n">
-        <v>63.9</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>36.9</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="7">
@@ -1881,22 +2012,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G7" t="n">
-        <v>28.1</v>
+        <v>44.6</v>
       </c>
       <c r="H7" t="n">
-        <v>100.9</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>63.9</v>
+        <v>63.7</v>
       </c>
       <c r="J7" t="n">
-        <v>36.9</v>
+        <v>28.7</v>
       </c>
     </row>
   </sheetData>
